--- a/Matriz_Trazabilidad.xlsx
+++ b/Matriz_Trazabilidad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\V I C T U S\OneDrive\Desktop\Entregable ingeniería de requisitos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roble\OneDrive\Desktop\Sexto Ciclo\Ingenieria-Requisitos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DFDFB7-71AE-4668-938D-BB783596F62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC03FDF9-B9A4-4C13-AF1F-C31516239A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz_Trazabilidad" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Necesidad (UR)</t>
   </si>
@@ -31,30 +31,18 @@
     <t>Caso de Uso (CU)</t>
   </si>
   <si>
-    <t>NEC-01 Respuesta rápida</t>
-  </si>
-  <si>
     <t>RF-001 Autenticar usuarios</t>
   </si>
   <si>
-    <t>CU-001 Registrar solicitud bancaria</t>
-  </si>
-  <si>
     <t>RF-002 Mostrar funcionalidades según rol</t>
   </si>
   <si>
     <t>RF-003 Registrar solicitudes bancarias</t>
   </si>
   <si>
-    <t>NEC-02 Reducir tareas repetitivas</t>
-  </si>
-  <si>
     <t>RF-004 Gestionar solicitudes</t>
   </si>
   <si>
-    <t>CU-002 Aprobar solicitud bancaria</t>
-  </si>
-  <si>
     <t>RF-005 Gestionar documentos</t>
   </si>
   <si>
@@ -67,9 +55,6 @@
     <t>RF-007 Monitorear procesos operativos</t>
   </si>
   <si>
-    <t>CU-003 Consultar indicadores</t>
-  </si>
-  <si>
     <t>RF-008 Administrar usuarios y roles</t>
   </si>
   <si>
@@ -77,6 +62,33 @@
   </si>
   <si>
     <t>RF-010 Gestionar notificaciones</t>
+  </si>
+  <si>
+    <t>NEC-01 Procesar solicitudes más rápido</t>
+  </si>
+  <si>
+    <t>CU-001 Iniciar sesión</t>
+  </si>
+  <si>
+    <t>CU-002 Registrar solicitud bancaria</t>
+  </si>
+  <si>
+    <t>NEC-02 Reducir tareas manuales</t>
+  </si>
+  <si>
+    <t>CU-003 Gestionar solicitudes</t>
+  </si>
+  <si>
+    <t>CU-004 Validar documentos</t>
+  </si>
+  <si>
+    <t>CU-005 Aprobar o rechazar solicitud</t>
+  </si>
+  <si>
+    <t>CU-006 Monitorear procesos operativos</t>
+  </si>
+  <si>
+    <t>CU-007 Administrar usuarios y roles</t>
   </si>
 </sst>
 </file>
@@ -94,7 +106,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,9 +132,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,12 +443,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,114 +459,114 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Matriz_Trazabilidad.xlsx
+++ b/Matriz_Trazabilidad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roble\OneDrive\Desktop\Sexto Ciclo\Ingenieria-Requisitos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC03FDF9-B9A4-4C13-AF1F-C31516239A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566BC30D-5AC4-4FD8-860F-2A7C86C5BE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
